--- a/Plantilla_SIGMA.xlsx
+++ b/Plantilla_SIGMA.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76493F8C-A2E4-452F-85E2-7722C00603EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DA27B4-6129-41AA-BCBE-F3182CD9461C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATOS_APP" sheetId="1" r:id="rId1"/>
@@ -14,9 +14,6 @@
     <sheet name="calculos dashboard" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="27" r:id="rId5"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>ID_INFORME</t>
   </si>
@@ -87,23 +84,17 @@
     <t>Validación QC</t>
   </si>
   <si>
-    <t>Etiquetas de fila</t>
+    <t>NOK</t>
   </si>
   <si>
-    <t>Total general</t>
-  </si>
-  <si>
-    <t>Cuenta de ESTADO_INICIAL</t>
-  </si>
-  <si>
-    <t>(en blanco)</t>
+    <t>PENDIENTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +113,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -177,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -193,11 +190,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -228,10 +221,6 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[Plantilla_SIGMA.xlsx]calculos dashboard!TablaDinámica2</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
   <c:chart>
     <c:title>
       <c:overlay val="0"/>
@@ -264,64 +253,6 @@
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-ES"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -331,17 +262,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'calculos dashboard'!$B$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -354,27 +274,36 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'calculos dashboard'!$A$5:$A$6</c:f>
+              <c:f>'calculos dashboard'!$A$1:$A$2</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>(en blanco)</c:v>
+                  <c:v>NOK</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PENDIENTE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'calculos dashboard'!$B$5:$B$6</c:f>
+              <c:f>'calculos dashboard'!$B$1:$B$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C57C-4B74-B4A2-AB3A0EAC3C6A}"/>
+              <c16:uniqueId val="{00000000-D045-4F36-923E-290FF173774D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -388,11 +317,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1189758720"/>
-        <c:axId val="1189748640"/>
+        <c:axId val="1915660448"/>
+        <c:axId val="1915663328"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1189758720"/>
+        <c:axId val="1915660448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -435,7 +364,7 @@
             <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1189748640"/>
+        <c:crossAx val="1915663328"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -443,7 +372,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1189748640"/>
+        <c:axId val="1915663328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -494,7 +423,7 @@
             <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1189758720"/>
+        <c:crossAx val="1915660448"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -506,37 +435,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -578,22 +476,6 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
 </c:chartSpace>
 </file>
 
@@ -1145,26 +1027,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
+        <xdr:cNvPr id="3" name="Gráfico 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD6A4DE0-6499-080C-7133-4FC5291B2FD1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0647CF66-C81F-4C83-A9E1-96EFADC8A372}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -1179,1142 +1063,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Autor" refreshedDate="46141.584427662034" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="85" xr:uid="{6C658471-862D-4809-B675-402554B66B9E}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:J86" sheet="DATOS_APP"/>
-  </cacheSource>
-  <cacheFields count="10">
-    <cacheField name="ID_INFORME" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-    <cacheField name="FECHA" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-    <cacheField name="ZONA" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-    <cacheField name="DISCIPLINA" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-    <cacheField name="SUB_DISCIPLINA" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-    <cacheField name="EQUIPO" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-    <cacheField name="BLOQUE" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-    <cacheField name="DEFECTO" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-    <cacheField name="ESTADO_INICIAL" numFmtId="0">
-      <sharedItems containsNonDate="0" containsBlank="1" count="3">
-        <m/>
-        <s v="PENDIENTE" u="1"/>
-        <s v="NOK" u="1"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="OBSERVACIONES" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="85">
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="0"/>
-    <m/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD425414-AC8C-4D30-A1F5-64133C2F8ADD}" name="TablaDinámica2" cacheId="27" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A4:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="4">
-        <item m="1" x="2"/>
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de ESTADO_INICIAL" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3834,36 +2582,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2D57A8-9DAE-416C-BDFD-B93A511B7E45}">
-  <dimension ref="A3:B6"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="9"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="B1" s="7">
+        <f>COUNTIF(DATOS_APP!I:I, "NOK")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="9"/>
+      <c r="B2">
+        <f>COUNTIF(DATOS_APP!I:I, "PENDIENTE")</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
